--- a/artfynd/S 2801-2026 artfynd.xlsx
+++ b/artfynd/S 2801-2026 artfynd.xlsx
@@ -3029,7 +3029,7 @@
         <v>137225025</v>
       </c>
       <c r="B22" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
